--- a/output/xlsx/matriz_entrada_codificacion.xlsx
+++ b/output/xlsx/matriz_entrada_codificacion.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Impedir reservas sobre ejemplares ya reservados</t>
+          <t>Impedir reserva de ejemplar con reserva activa</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva</t>
+          <t>Mostrar confirmación de reserva registrada</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Actualizar información de préstamo</t>
+          <t>Actualizar información del préstamo</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Registrar mascota</t>
+          <t>Registrar Libro</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">

--- a/output/xlsx/matriz_entrada_codificacion.xlsx
+++ b/output/xlsx/matriz_entrada_codificacion.xlsx
@@ -430,7 +430,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Registrar reserva asociada al estudiante</t>
+          <t>Registrar reserva del ejemplar</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Pendiente de relación</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva registrada</t>
+          <t>Mostrar confirmación de reserva</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Pendiente de relación</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Registrar Libro</t>
+          <t>Registrar mascota</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">

--- a/output/xlsx/matriz_entrada_codificacion.xlsx
+++ b/output/xlsx/matriz_entrada_codificacion.xlsx
@@ -430,7 +430,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Impedir reserva de ejemplar con reserva activa</t>
+          <t>Impedir reservas duplicadas activas</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pendiente de relación</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pendiente de relación</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la disponibilidad inmediatamente después de confirmar una reserva.</t>
+          <t>El sistema deberá actualizar la disponibilidad del ejemplar inmediatamente después de confirmar una reserva.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
+          <t>Reservar un ejemplar disponible del catálogo de la biblioteca</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
+          <t>El sistema deberá reservar un ejemplar disponible del catálogo de la biblioteca.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
+          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
+          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
+          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos de la devolución sean correctos.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">

--- a/output/xlsx/matriz_entrada_codificacion.xlsx
+++ b/output/xlsx/matriz_entrada_codificacion.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad Diseño" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Diseño'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Diseño'!$A$1:$J$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -429,8 +429,8 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mostrar ejemplares disponibles para reserva</t>
+          <t>Consulta de ejemplares disponibles</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONFORME CON MEJORAS</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mostrar información del ejemplar antes de confirmar</t>
+          <t>Visualización de detalles del ejemplar</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CONFORME CON MEJORAS</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Registrar reserva del ejemplar</t>
+          <t>Registro de reserva</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONFORME CON MEJORAS</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cambiar estado del ejemplar a reservado</t>
+          <t>Actualización de estado del ejemplar</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONFORME CON MEJORAS</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Impedir reservas duplicadas activas</t>
+          <t>Bloqueo de reserva duplicada</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -721,27 +721,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02, ED-03</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva</t>
+          <t>Confirmación de reserva</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -773,27 +773,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-01</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Informar fecha límite de recogida</t>
+          <t>Información de fecha límite de recogida</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -825,27 +825,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -867,37 +867,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Actualización inmediata de disponibilidad</t>
+          <t>Inmediatez en la actualización de disponibilidad</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la disponibilidad del ejemplar inmediatamente después de confirmar una reserva.</t>
+          <t>El sistema deberá actualizar la disponibilidad inmediatamente después de confirmar una reserva.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02, ED-03</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -919,37 +919,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Reservar un ejemplar disponible del catálogo de la biblioteca</t>
+          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá reservar un ejemplar disponible del catálogo de la biblioteca.</t>
+          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02, ED-03</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -971,37 +971,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
+          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
+          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1023,37 +1023,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
+          <t>El sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
+          <t>El sistema deberá el sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02, ED-03</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1085,27 +1085,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-01, ED-02</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02, ED-03</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1189,27 +1189,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02, ED-04</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1241,27 +1241,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-01</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1283,37 +1283,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Continuar proceso con datos correctos</t>
+          <t>Permitir continuar proceso con datos correctos</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos de la devolución sean correctos.</t>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-01</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1345,27 +1345,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>DIS-002</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Pendiente de relación</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
         </is>
       </c>
     </row>
@@ -1397,27 +1397,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-03</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1449,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-03</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1501,32 +1501,448 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>DIS-002</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pendiente de relación</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RF-021</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Consultar historial de préstamos del estudiante</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar únicamente los préstamos asociados al estudiante autenticado que realiza la consulta.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ED-01, ED-02, ED-03</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RF-022</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ordenar historial de préstamos por fecha</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá presentar la lista de préstamos ordenada por fecha, del más reciente al más antiguo.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ED-01</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RF-023</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mostrar detalles del préstamo en el historial</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar para cada préstamo el título del libro, la fecha de préstamo, la fecha de devolución esperada y el estado actual.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ED-01</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RF-024</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Filtrar préstamos por estado</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir filtrar los préstamos del historial por estado.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ED-01</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RF-025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mostrar mensaje de historial vacío</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar un mensaje cuando el estudiante no tenga préstamos registrados.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ED-02</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RF-026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Impedir consulta de historial ajeno</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá impedir que un estudiante consulte el historial de otro estudiante.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pendiente de relación</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RF-027</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>La información mostrada debe reflejar el estado actual de cada préstamo</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la información mostrada debe reflejar el estado actual de cada préstamo.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pendiente de relación</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RF-028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No se permite la modificación de los registros desde esta consulta</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá no se permite la modificación de los registros desde esta consulta.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pendiente de relación</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_codificacion.xlsx
+++ b/output/xlsx/matriz_entrada_codificacion.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad Diseño" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Diseño'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Diseño'!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Consulta de ejemplares disponibles</t>
+          <t>Mostrar ejemplares disponibles para reserva</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -513,27 +513,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ED-01, ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Visualización de detalles del ejemplar</t>
+          <t>Mostrar detalles del ejemplar antes de confirmar reserva</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -607,37 +607,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Registro de reserva</t>
+          <t>Registrar reserva asociada al estudiante autenticado</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ED-02, ED-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Actualización de estado del ejemplar</t>
+          <t>Cambiar estado del ejemplar a reservado</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -669,27 +669,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ED-02, ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bloqueo de reserva duplicada</t>
+          <t>Impedir reserva de ejemplar con reserva activa</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -721,27 +721,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ED-02, ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Confirmación de reserva</t>
+          <t>Mostrar confirmación de reserva registrada</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -773,27 +773,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Información de fecha límite de recogida</t>
+          <t>Informar fecha límite para recoger ejemplar</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -825,27 +825,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -867,37 +867,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Inmediatez en la actualización de disponibilidad</t>
+          <t>Reservar un ejemplar disponible del catálogo de la biblioteca</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la disponibilidad inmediatamente después de confirmar una reserva.</t>
+          <t>El sistema deberá reservar un ejemplar disponible del catálogo de la biblioteca.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ED-02, ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -929,27 +929,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ED-02, ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -971,37 +971,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
+          <t>La disponibilidad debe actualizarse inmediatamente después de confirmar una reserva</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
+          <t>El sistema deberá la disponibilidad debe actualizarse inmediatamente después de que el estudiante confirme una reserva.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ED-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
@@ -1023,44 +1023,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible</t>
+          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el sistema debe impedir la reserva cuando el ejemplar no se encuentre disponible.</t>
+          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DIS-001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ED-02, ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-001 – HU-001 - Reservar libro disponible</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Registrar devolución de libro</t>
+          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir registrar la devolución de un libro prestado.</t>
+          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ED-01, ED-02</t>
+          <t>ED-02, ED-03, ED-04</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>Requiere revisión</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Verificar préstamo relacionado</t>
+          <t>Registrar devolución de libro</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro al registrar su devolución.</t>
+          <t>El sistema deberá permitir registrar la devolución de un libro.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ED-02, ED-03</t>
+          <t>ED-01, ED-02, ED-04</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Actualizar información del préstamo</t>
+          <t>Verificar existencia de préstamo</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
+          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ED-02, ED-04</t>
+          <t>ED-02, ED-03</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de confirmación de devolución</t>
+          <t>Actualizar información del préstamo</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>ED-02, ED-04</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Permitir continuar proceso con datos correctos</t>
+          <t>Mostrar mensaje de devolución registrada</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>ED-01, ED-02</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Registrar mascota</t>
+          <t>Continuar proceso con datos correctos</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar mascota.</t>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-01</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pendiente de relación</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>El libro debe existir en el sistema</t>
+          <t>Registrar mascota</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el libro debe existir en el sistema.</t>
+          <t>El sistema deberá registrar mascota.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>La devolución debe corresponder a un préstamo registrado</t>
+          <t>El libro debe existir en el sistema</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+          <t>El sistema deberá el libro debe existir en el sistema.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-03</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pendiente de relación</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Consultar historial de préstamos del estudiante</t>
+          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar únicamente los préstamos asociados al estudiante autenticado que realiza la consulta.</t>
+          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ED-01, ED-02, ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>Requiere revisión</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ordenar historial de préstamos por fecha</t>
+          <t>Consultar historial de préstamos</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá presentar la lista de préstamos ordenada por fecha, del más reciente al más antiguo.</t>
+          <t>El sistema deberá consultar el historial de los préstamos que el estudiante autenticado ha realizado en la biblioteca.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>ED-01, ED-02, ED-03</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mostrar detalles del préstamo en el historial</t>
+          <t>Mostrar préstamos del estudiante autenticado</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar para cada préstamo el título del libro, la fecha de préstamo, la fecha de devolución esperada y el estado actual.</t>
+          <t>El sistema deberá mostrar únicamente los préstamos asociados al estudiante autenticado.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>Requiere revisión</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Filtrar préstamos por estado</t>
+          <t>Ordenar préstamos por fecha descendente</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir filtrar los préstamos del historial por estado.</t>
+          <t>El sistema deberá presentar la lista de préstamos ordenada por fecha, del más reciente al más antiguo.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>Requiere revisión</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de historial vacío</t>
+          <t>Mostrar detalles de cada préstamo</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando el estudiante no tenga préstamos registrados.</t>
+          <t>El sistema deberá mostrar para cada préstamo el título del libro, la fecha de préstamo, la fecha de devolución esperada y el estado actual (activo, devuelto, vencido).</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ED-02</t>
+          <t>ED-01</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>Requiere revisión</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Impedir consulta de historial ajeno</t>
+          <t>Filtrar préstamos por estado</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá impedir que un estudiante consulte el historial de otro estudiante.</t>
+          <t>El sistema deberá permitir filtrar los préstamos por estado.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-01</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pendiente de relación</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>La información mostrada debe reflejar el estado actual de cada préstamo</t>
+          <t>Mostrar mensaje sin préstamos</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la información mostrada debe reflejar el estado actual de cada préstamo.</t>
+          <t>El sistema deberá mostrar un mensaje cuando el estudiante no tenga préstamos registrados.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pendiente de relación</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
@@ -1907,42 +1907,146 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Impedir que un estudiante consulte el historial de otro estudiante</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá impedir que un estudiante consulte el historial de otro estudiante.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Requiere revisión</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RF-029</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>La información mostrada debe reflejar el estado actual de cada préstamo</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la información mostrada debe reflejar el estado actual de cada préstamo.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 Consultar historial</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>RF-030</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>No se permite la modificación de los registros desde esta consulta</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>El sistema deberá no se permite la modificación de los registros desde esta consulta.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DIS-003</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Pendiente de relación</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>CORREGIR</t>
-        </is>
-      </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/xlsx/matriz_entrada_codificacion.xlsx
+++ b/output/xlsx/matriz_entrada_codificacion.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad Diseño" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Diseño'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Diseño'!$A$1:$J$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,18 +418,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,44 +503,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mostrar ejemplares disponibles para reserva</t>
+          <t>Registrar ejemplar asociado a libro y sucursal</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar únicamente los ejemplares que se encuentren disponibles para reserva.</t>
+          <t>El sistema deberá permitir registrar un ejemplar asociándolo a un libro y sucursal existentes, asignando automáticamente el estado inicial "disponible" y registrando su condición física.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-01, ED-02, ED-04</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -555,44 +555,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mostrar detalles del ejemplar antes de confirmar reserva</t>
+          <t>Generar código de identificación automático</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar el título, autor, categoría y código del ejemplar antes de confirmar la reserva.</t>
+          <t>El sistema deberá generar automáticamente el código de identificación del ejemplar con el formato bib-{sucursal}-{categoría}-{secuencial}.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Requiere revisión</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -607,44 +607,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Registrar reserva asociada al estudiante autenticado</t>
+          <t>Dar de baja un ejemplar registrando el motivo</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado.</t>
+          <t>El sistema deberá permitir dar de baja un ejemplar registrando el motivo correspondiente.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-02</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,44 +659,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cambiar estado del ejemplar a reservado</t>
+          <t>Impedir dar de baja un ejemplar prestado o dado de baja</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá cambiar el estado del ejemplar de disponible a reservado inmediatamente después de confirmar la reserva.</t>
+          <t>El sistema deberá impedir dar de baja un ejemplar que se encuentre actualmente prestado o ya dado de baja.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-06</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -711,44 +711,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Impedir reserva de ejemplar con reserva activa</t>
+          <t>Consultar ejemplares asociados a un libro específico</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá impedir que otro estudiante reserve un ejemplar que ya tenga una reserva activa.</t>
+          <t>El sistema deberá permitir consultar los ejemplares asociados a un libro específico con su estado actual.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-06, ED-08</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -763,44 +763,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva registrada</t>
+          <t>El libro y la sucursal deben existir previamente en el sistema</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar una confirmación cuando la reserva se registre correctamente.</t>
+          <t>El sistema deberá el libro y la sucursal deben existir previamente en el sistema.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-004</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -815,49 +815,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Informar fecha límite para recoger ejemplar</t>
+          <t>El código de ejemplar debe ser único en todo el sistema</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá informar al estudiante la fecha límite establecida para recoger el ejemplar reservado.</t>
+          <t>El sistema deberá el código de ejemplar debe ser único en todo el sistema.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-003</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-10</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RF-008</t>
+          <t>RF-007</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,49 +867,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Reservar un ejemplar disponible del catálogo de la biblioteca</t>
+          <t>El código de ejemplar debe ser único en todo el sistema</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá reservar un ejemplar disponible del catálogo de la biblioteca.</t>
+          <t>El sistema deberá el código de ejemplar debe ser único en todo el sistema.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-004</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RF-009</t>
+          <t>RF-008</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -919,49 +919,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Un ejemplar solo puede tener una reserva activa simultáneamente</t>
+          <t>El secuencial del código se genera automáticamente por sucursal y categoría</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá un ejemplar solo puede tener una reserva activa simultáneamente.</t>
+          <t>El sistema deberá el secuencial del código se genera automáticamente por sucursal y categoría.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-003</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-10</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RF-010</t>
+          <t>RF-009</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -971,49 +971,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>La disponibilidad debe actualizarse inmediatamente después de confirmar una reserva</t>
+          <t>Registrar préstamo de ejemplar a lector</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la disponibilidad debe actualizarse inmediatamente después de que el estudiante confirme una reserva.</t>
+          <t>El sistema deberá permitir registrar un préstamo seleccionando un ejemplar disponible y un lector.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-005</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ED-15, ED-16, ED-17</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RF-011</t>
+          <t>RF-010</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>La reserva debe quedar asociada al estudiante que realizó la operación</t>
+          <t>Verificar estado disponible del ejemplar</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la reserva debe quedar asociada al estudiante que realizó la operación.</t>
+          <t>El sistema deberá verificar que el ejemplar se encuentre en estado disponible antes de registrar el préstamo.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HU-001 – HU-001 - Reservar libro disponible</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RF-012</t>
+          <t>RF-011</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1075,74 +1075,74 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>La operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación</t>
+          <t>Verificar que el lector esté activo</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la operación de reserva debe utilizar la disponibilidad actual del ejemplar. Se debe registrar el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá verificar que el lector esté activo en el sistema.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ED-02, ED-03, ED-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Requiere revisión</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RF-013</t>
+          <t>RNF-001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Registrar devolución de libro</t>
+          <t>Verificar límite máximo de préstamos activos del lector</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir registrar la devolución de un libro.</t>
+          <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ED-01, ED-02, ED-04</t>
+          <t>ED-02</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
@@ -1164,27 +1164,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RF-014</t>
+          <t>RNF-001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Verificar existencia de préstamo</t>
+          <t>Verificar límite máximo de préstamos activos del lector</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá verificar que exista un préstamo relacionado con el libro.</t>
+          <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ED-02, ED-03</t>
+          <t>ED-06</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr">
@@ -1216,37 +1216,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RF-015</t>
+          <t>RNF-001</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Actualizar información del préstamo</t>
+          <t>Verificar límite máximo de préstamos activos del lector</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+          <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>DIS-003</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ED-02, ED-04</t>
+          <t>ED-10</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RF-016</t>
+          <t>RF-012</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1283,49 +1283,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mostrar mensaje de devolución registrada</t>
+          <t>Impedir préstamo cuando el lector tenga préstamos vencidos</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+          <t>El sistema deberá impedir el préstamo cuando el lector tenga préstamos vencidos sin devolver.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ED-01, ED-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RF-017</t>
+          <t>RF-013</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1335,49 +1335,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Continuar proceso con datos correctos</t>
+          <t>Calcular fecha de devolución esperada</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+          <t>El sistema deberá calcular automáticamente la fecha de devolución esperada según los días configurados.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RF-018</t>
+          <t>RF-014</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Registrar mascota</t>
+          <t>Cambiar estado del ejemplar a 'prestado'</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar mascota.</t>
+          <t>El sistema deberá cambiar el estado del ejemplar a "prestado" inmediatamente después de registrar el préstamo.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1407,29 +1407,29 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RF-019</t>
+          <t>RF-015</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1439,49 +1439,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>El libro debe existir en el sistema</t>
+          <t>Registrar bibliotecario que realizó la operación</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá el libro debe existir en el sistema.</t>
+          <t>El sistema deberá registrar el bibliotecario que realizó la operación.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RF-020</t>
+          <t>RF-016</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1491,49 +1491,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>La devolución debe corresponder a un préstamo registrado</t>
+          <t>Solo los bibliotecarios y administradores pueden registrar préstamos</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+          <t>El sistema deberá solo los bibliotecarios y administradores pueden registrar préstamos.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DIS-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ED-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HU-002 – HU-002 - Registrar préstamo de libro</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RF-021</t>
+          <t>RF-017</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+          <t>Un lector puede tener como máximo 3 préstamos activos simultáneamente</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+          <t>El sistema deberá un lector puede tener como máximo 3 préstamos activos simultáneamente.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DIS-003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1563,54 +1563,54 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Requiere revisión</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RF-022</t>
+          <t>RNF-002</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Consultar historial de préstamos</t>
+          <t>El plazo máximo de préstamo es de 15 días</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá consultar el historial de los préstamos que el estudiante autenticado ha realizado en la biblioteca.</t>
+          <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DIS-003</t>
+          <t>DIS-001</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ED-01, ED-02, ED-03</t>
+          <t>ED-02</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr">
@@ -1632,79 +1632,79 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RF-023</t>
+          <t>RNF-002</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mostrar préstamos del estudiante autenticado</t>
+          <t>El plazo máximo de préstamo es de 15 días</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar únicamente los préstamos asociados al estudiante autenticado.</t>
+          <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DIS-003</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>ED-06</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Requiere revisión</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>CONFORME</t>
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RF-024</t>
+          <t>RNF-002</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Funcional</t>
+          <t>No funcional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ordenar préstamos por fecha descendente</t>
+          <t>El plazo máximo de préstamo es de 15 días</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá presentar la lista de préstamos ordenada por fecha, del más reciente al más antiguo.</t>
+          <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1714,34 +1714,34 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>ED-10</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Requiere revisión</t>
+          <t>Cubierto en Diseño</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
+          <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RF-025</t>
+          <t>RF-018</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1751,49 +1751,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mostrar detalles de cada préstamo</t>
+          <t>No se permiten préstamos a lectores con devoluciones pendientes vencidas</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar para cada préstamo el título del libro, la fecha de préstamo, la fecha de devolución esperada y el estado actual (activo, devuelto, vencido).</t>
+          <t>El sistema deberá no se permiten préstamos a lectores con devoluciones pendientes vencidas.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DIS-003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Requiere revisión</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RF-026</t>
+          <t>RF-019</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1803,49 +1803,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Filtrar préstamos por estado</t>
+          <t>El identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá permitir filtrar los préstamos por estado.</t>
+          <t>El sistema deberá el identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DIS-003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ED-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RF-027</t>
+          <t>RF-020</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1855,49 +1855,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mostrar mensaje sin préstamos</t>
+          <t>Buscar libros por término, categoría o sucursal</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá mostrar un mensaje cuando el estudiante no tenga préstamos registrados.</t>
+          <t>El sistema deberá permitir buscar libros por título, autor o isbn utilizando un término de búsqueda.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DIS-003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ED-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Cubierto en Diseño</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con evidencia suficiente.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RF-028</t>
+          <t>RF-021</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Impedir que un estudiante consulte el historial de otro estudiante</t>
+          <t>Filtrar resultados por categoría y sucursal</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá impedir que un estudiante consulte el historial de otro estudiante.</t>
+          <t>El sistema deberá permitir filtrar los resultados por categoría del libro y por sucursal con ejemplares disponibles.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DIS-003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1927,29 +1927,29 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Requiere revisión</t>
+          <t>No evaluado</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CORREGIR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>Relación identificada con confianza insuficiente para confirmarla.</t>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RF-029</t>
+          <t>RF-022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>La información mostrada debe reflejar el estado actual de cada préstamo</t>
+          <t>Mostrar cantidad de ejemplares disponibles</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá la información mostrada debe reflejar el estado actual de cada préstamo.</t>
+          <t>El sistema deberá mostrar la cantidad de ejemplares disponibles de cada libro en los resultados de búsqueda.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1996,57 +1996,1721 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HU-003 – HU-003 Consultar historial</t>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>RF-023</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Paginar resultados de búsqueda</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá paginar los resultados de búsqueda cuando excedan 20 registros.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RF-024</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Consultar disponibilidad detallada por sucursal</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir consultar la disponibilidad detallada de un libro mostrando por cada sucursal el total de ejemplares y la cantidad disponible.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RF-025</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RNF-003</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Disponibilidad de información en tiempo real</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DIS-001</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ED-02</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RNF-003</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Disponibilidad de información en tiempo real</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DIS-002</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ED-06, ED-08</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RNF-003</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Disponibilidad de información en tiempo real</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>DIS-003</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ED-10</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CONFORME CON MEJORAS</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RNF-003</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Disponibilidad de información en tiempo real</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DIS-005</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ED-16, ED-17</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CORREGIR</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RF-026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>La búsqueda utiliza coincidencia parcial para permitir resultados aproximados</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la búsqueda utiliza coincidencia parcial para permitir resultados aproximados.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RNF-004</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Disponibilidad de información en tiempo real</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la búsqueda utiliza coincidencia parcial (ilike) para permitir resultados aproximados. La disponibilidad se calcula en tiempo real consultando el estado actual de los ejemplares.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DIS-004</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ED-13</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Cubierto en Diseño</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CONFORME CON MEJORAS</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>Relación identificada con evidencia suficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RF-027</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Registrar la devolución de un ejemplar prestado</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar la devolución de un ejemplar prestado.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RF-028</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Verificar existencia de préstamo activo</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que exista un préstamo activo relacionado con el ejemplar.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RF-029</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Actualizar información del préstamo después de la devolución</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>RF-030</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>No se permite la modificación de los registros desde esta consulta</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>El sistema deberá no se permite la modificación de los registros desde esta consulta.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mostrar mensaje de devolución registrada</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RF-031</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Continuar proceso con datos correctos</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RF-032</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>El ejemplar debe existir en el sistema</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el ejemplar debe existir en el sistema.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RF-033</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RF-034</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>RF-035</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Solicitar transferencia de ejemplar disponible</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir solicitar la transferencia de un ejemplar disponible.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RF-036</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Verificar disponibilidad del ejemplar</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que el ejemplar se encuentre disponible.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RF-037</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Registrar sucursal de origen y destino</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá registrar la sucursal de origen y la sucursal de destino.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RF-038</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RF-039</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>El ejemplar debe estar disponible</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el ejemplar debe estar disponible.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RF-040</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Las sucursales de origen y destino deben ser diferentes</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá las sucursales de origen y destino deben ser diferentes.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RF-041</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RF-042</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Registrar un libro con datos bibliográficos</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar un libro con título, autor, isbn, editorial, año de publicación y categoría.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RF-043</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Validar formato y unicidad de isbn</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá validar que el isbn sea único en el sistema y tenga un formato correcto (isbn-10 o isbn-13).</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RF-044</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Modificar la información bibliográfica de un libro existente</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir modificar la información bibliográfica de un libro existente.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RF-045</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Consultar libros aplicando filtros por título, autor y categoría</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir consultar libros aplicando filtros por título, autor y categoría.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RF-046</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mostrar la cantidad de ejemplares asociados al consultar un libro</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar la cantidad de ejemplares asociados al consultar un libro.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RF-047</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Paginar los resultados de la consulta cuando existan más de 20 libros</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá paginar los resultados de la consulta cuando existan más de 20 libros.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RF-048</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>La categoría del libro debe pertenecer al conjunto predefinido del sistema</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la categoría del libro debe pertenecer al conjunto predefinido del sistema.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RF-049</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>No se permite registrar dos libros con el mismo ISBN</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá no se permite registrar dos libros con el mismo ISBN.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RF-050</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>El libro debe estar registrado antes de poder crear ejemplares físicos asociados</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el libro debe estar registrado antes de poder crear ejemplares físicos asociados.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="inlineStr">
         <is>
           <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>